--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D78FB0B7-617F-4778-A123-3ED4049230CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B1C7C2-B9BD-4321-9BF4-065D004E2A3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="servicios" sheetId="1" r:id="rId1"/>
@@ -21,22 +21,23 @@
     <definedName name="listaS">datos!$C$2:$C$3</definedName>
     <definedName name="listaServicios">datos!$B$2:$B$10</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="173">
   <si>
     <t>Laboratorio</t>
   </si>
   <si>
+    <t>Contacto</t>
+  </si>
+  <si>
     <t>Servicio</t>
+  </si>
+  <si>
+    <t>Requiere Equipo del Laboratorio</t>
   </si>
   <si>
     <t>Descripcion y Alcance</t>
@@ -66,13 +67,13 @@
     <t>Herbario Henrí Alaín Liogie</t>
   </si>
   <si>
-    <t>Servicios</t>
+    <t>Santa Feliz herbario@unphu.edu.do</t>
   </si>
   <si>
     <t>Consultoria</t>
   </si>
   <si>
-    <t>Capacitacion</t>
+    <t>Si</t>
   </si>
   <si>
     <t>Asesoría técnica y levantamiento de información sobre la composición florística de un área mediante muestreos de campo, elaboración de listados de especies e informes técnicos para proyectos ambientales, de investigación, conservación o restauración ecológica.</t>
@@ -100,6 +101,9 @@
 cubrir los gastos logísticos cuando corresponda.</t>
   </si>
   <si>
+    <t>Capacitacion</t>
+  </si>
+  <si>
     <t>Capacitación teórico-práctica sobre técnicas de
  colecta, preservación, prensado, montaje, etiquetado y conservación de especímenes botánicos para investigación y docencia.</t>
   </si>
@@ -125,15 +129,6 @@
     <t>Requiere un número mínimo de participantes y un espacio adecuado para las actividades prácticas.</t>
   </si>
   <si>
-    <t>Si/no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
     <t>Planificación y desarrollo de actividades prácticas
  para el aprendizaje de técnicas de muestreo, colecta, observación e identificación de la flora en campo.</t>
   </si>
@@ -159,6 +154,9 @@
     <t>El contratante deberá gestionar los permisos y cubrir los gastos logísticos necesarios para la actividad.</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Charlas técnicas o de divulgación sobre 
 especies de interés, adaptadas al público objetivo.</t>
   </si>
@@ -197,10 +195,10 @@
     <t>El cliente deberá suministrar el listado en formato digital editable. El servicio no incluye la verificación de identificaciones mediante revisión de especímenes físicos.</t>
   </si>
   <si>
-    <t>Contacto</t>
-  </si>
-  <si>
-    <t>Santa Feliz herbario@unphu.edu.do</t>
+    <t>Laboratorio de Investigaciones en Ciencias Básicas</t>
+  </si>
+  <si>
+    <t>Alberto Nuñez: alnunez@unphu.edu.do</t>
   </si>
   <si>
     <t>Analisis Quimico</t>
@@ -209,13 +207,16 @@
     <t>Determinación del contenido de polifenoles en extractos de productos naturales por espectrofotometría UV-VIS</t>
   </si>
   <si>
-    <t>Laboratorio de Investigaciones en Ciencias Básicas</t>
-  </si>
-  <si>
-    <t>Requiere Equipo del Laboratorio</t>
-  </si>
-  <si>
-    <t>Alberto Nuñez: alnunez@unphu.edu.do</t>
+    <t>Farmaceuticas, Laboratorios</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas (pendiente de contracion)</t>
   </si>
   <si>
     <t>Determinación de polifenoles en extractos de productos naturales por cromatografía líquida de alta resolución (HPLC).</t>
@@ -239,6 +240,12 @@
     <t>Valorización del aprovechamiento de residuos agroalimentarios y forestales para la producción de productos de alto valor agregado.</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Implementación de Sistemas de Garantía de Calidad para el Análisis y Control de Procesos Productivos.</t>
   </si>
   <si>
@@ -251,33 +258,24 @@
     <t>Análisis del Estado del Arte, Nichos de Mercado y Direcciones Estratégicas de Investigación en Ciencias Básicas y Aplicadas.</t>
   </si>
   <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Laboratorio de Investigación de Ciencias Biológicas</t>
   </si>
   <si>
     <t>Enmanuel Antonio Montero emontero@unphu.edu.do</t>
   </si>
   <si>
+    <t>Servicio 1. Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
+  </si>
+  <si>
     <t>Consultoras ambientales, empresas de la pesca ornamental y acuicolas, instituciones públicas, ONG, universidades,  investigadores</t>
   </si>
   <si>
-    <t>Servicio 1. Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros
+Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
   </si>
   <si>
     <t xml:space="preserve">Reactivos y materiales/cristaleria
  para colecta y preservación de muestras. </t>
-  </si>
-  <si>
-    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros
-Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
   </si>
   <si>
     <t>Expertos en biología pesquera y biología de conservación, 
@@ -316,6 +314,9 @@
  material de montaje de especímenes. </t>
   </si>
   <si>
+    <t xml:space="preserve">Experta en biologia molecular  </t>
+  </si>
+  <si>
     <t>Servicio 4.Amplifición  de ADN (Tejidos y eDNA)</t>
   </si>
   <si>
@@ -323,40 +324,34 @@
  material de montaje de especímenes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Experta en biologia molecular  </t>
-  </si>
-  <si>
     <t>Taller técnicas de muestreo de campo en investigaciones de especies marinas pesqueras</t>
   </si>
   <si>
+    <t>Instituciones públicas y privadas, universidades y publico en general</t>
+  </si>
+  <si>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros</t>
+  </si>
+  <si>
+    <t>Material didáctico y recursos audiovisuales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
+  </si>
+  <si>
     <t>Bases para el diseño metodológico de técnicas moleculares para estudios de macrofauna</t>
   </si>
   <si>
-    <t>Instituciones públicas y privadas, universidades y publico en general</t>
-  </si>
-  <si>
-    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros</t>
-  </si>
-  <si>
     <t>Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
   </si>
   <si>
-    <t>Material didáctico y recursos audiovisuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Laboratorio de Investigaciones de la Facultad de Ciencias y Tecnología</t>
   </si>
   <si>
+    <t>Ramón Alonso Pérez Romero rperez@unphu.edu.do</t>
+  </si>
+  <si>
     <t>Análisis de composición</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Laboratorio de Ciencias y Tecnología</t>
-  </si>
-  <si>
-    <t>Ramón Alonso Pérez Romero rperez@unphu.edu.do</t>
   </si>
   <si>
     <t>Determinación de los parámetros de composición proximal (humedad, cenizas, proteína cruda, grasa cruda, fibra cruda/NDF/ADF/ADL y carbohidratos por diferencia) en muestras alimenticias, agropecuarias o materias primas, mediante métodos estandarizados. Incluye preparación de la muestra, ejecución del análisis y entrega de reporte de resultados.</t>
@@ -382,13 +377,202 @@
     <t xml:space="preserve"> No se aceptan muestras de carnes, pescados u otros productos de origen cárnico/pesquero. El laboratorio está enfocado prioritariamente en la valorización de biomasa residual y alimentos poco convencionales.</t>
   </si>
   <si>
-    <t>Farmaceuticas, Laboratorios</t>
-  </si>
-  <si>
-    <t>Personal del Laboratorio</t>
-  </si>
-  <si>
-    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas (pendiente de contracion)</t>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Si/no</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Laboratorio de Ciencias y Tecnología</t>
+  </si>
+  <si>
+    <t>Laboratorio de Investigaciones Odontológicas (LABIO)</t>
+  </si>
+  <si>
+    <t>Cultivo celular</t>
+  </si>
+  <si>
+    <t>Evaluación de citotoxicidad in vitro de biomateriales y productos odontológicos. Evaluación in vitro de la biocompatibilidad de materiales dentales mediante cultivo celular. Exposición de células en cultivo a materiales, extractos o eluados (resinas, cementos, selladores, adhesivos, irrigantes, colutorios, etc.) y evaluación de la viabilidad celular por conteo con azul de tripano y de la morfología celular por microscopía invertida con registro fotográfico. Incluye preparación de extractos, siembra, exposición, conteo, documentación fotográfica e informe técnico con resultados.</t>
+  </si>
+  <si>
+    <t>Empresas y distribuidores de materiales dentales, investigadores, estudiantes de pregrado y posgrado, clínicas y otros laboratorios universitarios.</t>
+  </si>
+  <si>
+    <t>Campana de flujo laminar, incubadora de CO₂, contador de células, microscopio invertido con cámara, centrífuga, baño María y balanza.</t>
+  </si>
+  <si>
+    <t>Medio de cultivo, suero fetal bovino, antibióticos, tripsina, PBS, azul de tripano, placas y frascos de cultivo estériles, puntas y pipetas serológicas, material de bioseguridad (guantes y desinfectantes).</t>
+  </si>
+  <si>
+    <t>Investigador con formación en cultivo celular (responsable técnico) y un técnico o asistente capacitado.</t>
+  </si>
+  <si>
+    <t>De 1 a 3 días hábiles para revisión de la solicitud. De 5 a 10 días hábiles para el ensayo, según el número de materiales, tiempos de exposición y réplicas; y de 2 a 3 días hábiles para el informe.</t>
+  </si>
+  <si>
+    <t>Ensayo de cribado preliminar; no sustituye la certificación regulatoria de un producto. Servicio realizado únicamente en LABIO. Se utilizan las líneas celulares disponibles en el laboratorio; el cliente no podrá introducir material biológico propio sin acuerdo previo. El cliente entrega el material con ficha técnica y hoja de seguridad. No se aceptan sustancias tóxicas no declaradas. Resultados limitados a los ensayos disponibles. El diseño experimental, los tiempos y las condiciones de muestreo se acuerdan previamente con el laboratorio.</t>
+  </si>
+  <si>
+    <t>Servicio de cultivo celular y documentación microscópica: mantenimiento, expansión y conteo de cultivos celulares con registro fotográfico. Incluye mantenimiento de cultivos, subcultivo (pases), expansión, conteo y evaluación de viabilidad y confluencia, con captura de imágenes de microscopía invertida a distintos tiempos. Entrega de reporte de crecimiento y archivo de imágenes.</t>
+  </si>
+  <si>
+    <t>Investigadores, estudiantes de pregrado y posgrado, otros centros de investigación y empresas que requieran apoyo en cultivo celular.</t>
+  </si>
+  <si>
+    <t>Campana de flujo laminar, incubadora de CO₂, microscopio invertido con cámara, contador de células, centrífuga y baño María.</t>
+  </si>
+  <si>
+    <t>Medios y suplementos, tripsina, PBS, azul de tripano, plásticos de cultivo estériles, desinfectantes y material de protección personal.</t>
+  </si>
+  <si>
+    <t>Técnico o investigador con experiencia en técnica aséptica y cultivo celular.</t>
+  </si>
+  <si>
+    <t>Por sesión de trabajo, de 2 a 4 horas. El servicio completo depende de la duración del cultivo (de días a semanas).</t>
+  </si>
+  <si>
+    <t>Capacidad limitada por disponer de una sola incubadora de CO₂. Solo se aceptan líneas celulares previamente aprobadas y con certificado de origen. No se manejará material con riesgo biológico alto. Las agendas se asignan por disponibilidad. El servicio no incluye ensayos moleculares ni criopreservación.</t>
+  </si>
+  <si>
+    <t>Análisis de pH, calcio y flúor en muestras líquidas y materiales. Determinación de pH y concentración de calcio y flúor en soluciones, saliva y eluados de materiales dentales. Medición con multiparámetro en muestras acuosas: colutorios, dentífricos diluidos, soluciones de remineralización, saliva y medios de inmersión de materiales dentales (liberación iónica). Incluye calibración del equipo, medición con réplicas e informe de resultados.</t>
+  </si>
+  <si>
+    <t>Industria de productos de higiene oral, investigadores, estudiantes de pregrado y posgrado y clínicas.</t>
+  </si>
+  <si>
+    <t>Multiparámetro (pH, calcio, flúor), balanza, vortex, centrífuga y baño María.</t>
+  </si>
+  <si>
+    <t>Soluciones estándar y buffers de calibración, soluciones ajustadoras de fuerza iónica (TISAB), agua desionizada, recipientes y puntas, material de limpieza de electrodos y cristalería.</t>
+  </si>
+  <si>
+    <t>Técnico o investigador con formación en química analítica o ciencias biológicas.</t>
+  </si>
+  <si>
+    <t>De 1 a 2 horas por tanda de muestras, más 2 a 3 días hábiles para el informe.</t>
+  </si>
+  <si>
+    <t>Solo muestras líquidas o extractos acuosos. Volumen mínimo de muestra y condiciones de conservación a acordar. Las muestras biológicas (saliva) solo se aceptan con consentimiento informado y bajo condiciones de bioseguridad. No se analizan muestras corrosivas o peligrosas no declaradas.</t>
+  </si>
+  <si>
+    <t>Arrendamiento de equipos</t>
+  </si>
+  <si>
+    <t>Uso asistido de equipos de cultivo celular, análisis u otros. Uso supervisado de equipos de laboratorio por hora o por sesión. Acceso a campana de flujo laminar, centrífuga, contador de células, microscopio invertido con cámara, baño María, vortex, multiparámetro u otros, siempre con personal del laboratorio presente o con usuarios previamente capacitados y autorizados.</t>
+  </si>
+  <si>
+    <t>Investigadores externos, estudiantes de pregrado y posgrado y otros laboratorios o proyectos.</t>
+  </si>
+  <si>
+    <t>Campana de flujo laminar, centrífuga, contador de células, microscopio invertido con cámara, baño María, vortex, multiparámetro u otros equipos, según la solicitud.</t>
+  </si>
+  <si>
+    <t>A cargo del usuario, salvo acuerdo contrario. El laboratorio puede proveer insumos con costo adicional.</t>
+  </si>
+  <si>
+    <t>Técnico supervisor del laboratorio.</t>
+  </si>
+  <si>
+    <t>Bloques de 2 a 4 horas, sujetos a reserva previa.</t>
+  </si>
+  <si>
+    <t>Los equipos no pueden salir de la universidad. El uso está condicionado a una inducción en bioseguridad y buenas prácticas. El usuario acepta las normas del laboratorio, horarios y disponibilidad, y es responsable de los daños por mal uso. Se prohíbe el uso de material biológico no autorizado.</t>
+  </si>
+  <si>
+    <t>Consultoría científica y técnica en investigación odontológica. Asesoría en diseño de estudios in vitro u otros, evaluación de biomateriales y bioseguridad. Apoyo en diseño experimental, selección de ensayos de biocompatibilidad y fisicoquímicos, elaboración de protocolos, interpretación de resultados, redacción de secciones metodológicas y orientación sobre bioseguridad y manejo de muestras biológicas.</t>
+  </si>
+  <si>
+    <t>Empresas del sector salud, clínicas, investigadores y estudiantes de pregrado o posgrado.</t>
+  </si>
+  <si>
+    <t>No requiere equipos. Se presta en oficina o laboratorio.</t>
+  </si>
+  <si>
+    <t>No requiere reactivos.</t>
+  </si>
+  <si>
+    <t>Investigador con formación en ciencias biológicas y áreas afines, con experiencia en investigación odontológica.</t>
+  </si>
+  <si>
+    <t>Reunión inicial de 1 a 2 horas; entrega de informe o protocolo en 5 a 10 días hábiles según complejidad.</t>
+  </si>
+  <si>
+    <t>No constituye certificación ni asesoría clínica. Se firma acuerdo de confidencialidad cuando aplique. Los alcances se definen en una propuesta previa.</t>
+  </si>
+  <si>
+    <t>Banco y Biobanco de Dientes Humanos Dr. Eduardo Khouri Diep</t>
+  </si>
+  <si>
+    <t>Radiografía digital</t>
+  </si>
+  <si>
+    <t>Radiografía digital de muestras dentales. Captura de imágenes radiográficas digitales de dientes extraídos y modelos para observar anatomía radicular, número y curvatura de conductos, obturaciones y resultados de instrumentación o tratamientos experimentales. Incluye entrega de imágenes en formato digital e informe descriptivo básico.</t>
+  </si>
+  <si>
+    <t>Investigadores, estudiantes de pregrado y posgrado, empresas de instrumental endodóntico y clínicos.</t>
+  </si>
+  <si>
+    <t>Radiovisiógrafo con tablet integrada; fuente de rayos X o equipo de radiología disponible.</t>
+  </si>
+  <si>
+    <t>Barreras de protección del sensor, soportes de posicionamiento y material de bioseguridad.</t>
+  </si>
+  <si>
+    <t>Personal capacitado en radiología odontológica y protección radiológica.</t>
+  </si>
+  <si>
+    <t>De 15 a 30 minutos por muestra; entrega de archivos en 3 a 5 días hábiles.</t>
+  </si>
+  <si>
+    <t>Solo muestras dentales extraídas, previamente desinfectadas. Sujeto a las normas de protección radiológica. El equipo no sale de la institución.</t>
+  </si>
+  <si>
+    <t>Pruebas endodónticas</t>
+  </si>
+  <si>
+    <t>Instrumentación endodóntica ex vivo y pruebas experimentales en dientes extraídos. Preparación biomecánica de conductos radiculares ex vivo con motores endodónticos X-Smart de Dentsply y Eighteeth, para evaluar sistemas de limas, secuencias de instrumentación, tiempos de trabajo y resultados radiográficos. Incluye selección y preparación de dientes, instrumentación, radiografía de control e informe.</t>
+  </si>
+  <si>
+    <t>Fabricantes y distribuidores de instrumental endodóntico, investigadores, estudiantes de pregrado y posgrado y programas de especialidad.</t>
+  </si>
+  <si>
+    <t>Motores endodónticos X-Smart y Eighteeth, radiovisiógrafo, microscopio binocular, ultrasonido y nevera.</t>
+  </si>
+  <si>
+    <t>Limas y sistemas aportados por el cliente o por el laboratorio, irrigantes, jeringas, agujas, material de protección y dientes del biobanco.</t>
+  </si>
+  <si>
+    <t>Odontólogo o endodoncista investigador y un asistente técnico.</t>
+  </si>
+  <si>
+    <t>De 1 a 3 semanas según el tamaño de la muestra y el diseño del estudio.</t>
+  </si>
+  <si>
+    <t>Uso de dientes del biobanco con trazabilidad y aprobación ética vigente. Los resultados son experimentales ex vivo y no sustituyen estudios clínicos. El cliente debe entregar el material de prueba con ficha técnica.</t>
+  </si>
+  <si>
+    <t>Preparación de muestras</t>
+  </si>
+  <si>
+    <t>Preparación, limpieza y caracterización morfológica de dientes extraídos. Procesamiento de dientes extraídos y observación al microscopio. Limpieza, eliminación de tejidos blandos y cálculo mediante ultrasonido, desinfección según protocolo validado, clasificación morfológica y observación al microscopio óptico binocular, con registro de características (tipo de diente, estado, defectos, caries, desgaste, etc.). Entrega de muestras preparadas e informe de caracterización.</t>
+  </si>
+  <si>
+    <t>Investigadores, estudiantes de pregrado y posgrado y laboratorios de materiales dentales.</t>
+  </si>
+  <si>
+    <t>Equipo de limpieza ultrasónica, puntas ultrasónicas, microscopio binocular ZEISS Primotech y nevera.</t>
+  </si>
+  <si>
+    <t>Soluciones desinfectantes, solución salina, recipientes rotulados, material de bioseguridad, material de registro y solución de preservación.</t>
+  </si>
+  <si>
+    <t>Técnico capacitado en bioseguridad y manejo de muestras dentales.</t>
+  </si>
+  <si>
+    <t>De 3 a 5 días hábiles para lotes pequeños (hasta 30 dientes); los lotes mayores se acuerdan.</t>
+  </si>
+  <si>
+    <t>La observación microscópica es morfológica básica; no incluye histología ni microscopía electrónica. Solo se procesan dientes con consentimiento informado y documentación de origen.</t>
   </si>
 </sst>
 </file>
@@ -462,7 +646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -478,9 +662,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -495,7 +682,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
+          <bgColor theme="9" tint="-0.49995422223578601"/>
         </patternFill>
       </fill>
     </dxf>
@@ -562,7 +749,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -597,7 +784,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -641,23 +828,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -667,23 +854,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -691,26 +878,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -745,17 +929,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -772,149 +956,144 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.140625" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
     <col min="10" max="10" width="43.28515625" customWidth="1"/>
     <col min="11" max="11" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>30</v>
@@ -940,649 +1119,649 @@
     </row>
     <row r="5" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>91</v>
@@ -1591,65 +1770,65 @@
         <v>92</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="J23" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="J24" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>100</v>
@@ -1671,6 +1850,286 @@
       </c>
       <c r="K25" s="1" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="198" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="158.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="118.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="171.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1686,42 +2145,41 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A67" xr:uid="{D8DECFFA-5CBE-4E0D-8A27-6C55887A2999}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A67" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>listaLab</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C57" xr:uid="{70FEB337-C351-4F50-AE87-030127DE8B64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C57" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>listaServicios</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D57" xr:uid="{6CDCAB9A-F482-4EC0-9315-59F984EF0DA1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D57" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>listaS</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="alnunez@unphu.edu.do" xr:uid="{09C99202-9552-4F98-98DE-68801413754A}"/>
-    <hyperlink ref="B8" r:id="rId2" display="alnunez@unphu.edu.do" xr:uid="{0E1A8D9C-C515-4F57-ABCE-AA52629D9F07}"/>
-    <hyperlink ref="B9" r:id="rId3" display="alnunez@unphu.edu.do" xr:uid="{DE972DF2-4DD8-4D8F-B4B2-7A0338403B2B}"/>
-    <hyperlink ref="B10" r:id="rId4" display="alnunez@unphu.edu.do" xr:uid="{F71B584C-738D-4887-80E0-E9F5F028F305}"/>
-    <hyperlink ref="B11" r:id="rId5" display="alnunez@unphu.edu.do" xr:uid="{386440C9-B821-42E9-9C35-5596908D7430}"/>
-    <hyperlink ref="B12" r:id="rId6" display="alnunez@unphu.edu.do" xr:uid="{42B2DC46-29CD-44E2-8B7E-A27B705F6E73}"/>
-    <hyperlink ref="B13" r:id="rId7" display="alnunez@unphu.edu.do" xr:uid="{F1D91BA9-2B52-4E46-A7ED-66DA2697F52B}"/>
-    <hyperlink ref="B14" r:id="rId8" display="alnunez@unphu.edu.do" xr:uid="{86B1AF36-3D6A-4851-88EC-E15AD611FDC4}"/>
-    <hyperlink ref="B15" r:id="rId9" display="alnunez@unphu.edu.do" xr:uid="{110B4970-8F4A-4A14-A237-28D4756B4267}"/>
-    <hyperlink ref="B16" r:id="rId10" display="alnunez@unphu.edu.do" xr:uid="{72A6886C-C407-4FF8-A6A0-7D2F3242D502}"/>
-    <hyperlink ref="B17" r:id="rId11" display="alnunez@unphu.edu.do" xr:uid="{03313421-0E49-4646-BBB8-CE35126DA7FD}"/>
-    <hyperlink ref="B18" r:id="rId12" display="alnunez@unphu.edu.do" xr:uid="{D53364F5-C00F-4A56-B88F-FC46E4F052F5}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B15" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E6260D-E141-4E01-9DD9-6796BD13D20A}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1729,48 +2187,82 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B1C7C2-B9BD-4321-9BF4-065D004E2A3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D0B1C7C2-B9BD-4321-9BF4-065D004E2A3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{F4D732DA-A8BC-4733-980B-31EBF87E211B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="174">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>La observación microscópica es morfológica básica; no incluye histología ni microscopía electrónica. Solo se procesan dientes con consentimiento informado y documentación de origen.</t>
+  </si>
+  <si>
+    <t>nd9304@unphu.edu.do</t>
   </si>
 </sst>
 </file>
@@ -646,7 +649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -663,6 +666,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1856,8 +1862,8 @@
       <c r="A26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>55</v>
+      <c r="B26" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>111</v>
@@ -1891,8 +1897,8 @@
       <c r="A27" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>55</v>
+      <c r="B27" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>111</v>
@@ -1926,8 +1932,8 @@
       <c r="A28" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>55</v>
+      <c r="B28" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>52</v>
@@ -1961,8 +1967,8 @@
       <c r="A29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>55</v>
+      <c r="B29" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>133</v>
@@ -1996,8 +2002,8 @@
       <c r="A30" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>55</v>
+      <c r="B30" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>13</v>
@@ -2031,8 +2037,8 @@
       <c r="A31" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>55</v>
+      <c r="B31" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>149</v>
@@ -2066,8 +2072,8 @@
       <c r="A32" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>55</v>
+      <c r="B32" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>157</v>
@@ -2101,8 +2107,8 @@
       <c r="A33" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>55</v>
+      <c r="B33" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>165</v>
@@ -2168,6 +2174,8 @@
     <hyperlink ref="B16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="B17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="B18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B26" r:id="rId13" xr:uid="{F972F02D-A7D1-45B1-9625-8CD3762EF637}"/>
+    <hyperlink ref="B27:B33" r:id="rId14" display="nd9304@unphu.edu.do" xr:uid="{B87B9367-5431-4996-AA71-F3ABDCA9B1AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,28 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D0B1C7C2-B9BD-4321-9BF4-065D004E2A3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{F4D732DA-A8BC-4733-980B-31EBF87E211B}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{A5E38AE1-74D9-454B-9CB1-7972C456C45F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B34FE5E9-FA94-465E-8F1B-61D69017EE4F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="servicios" sheetId="1" r:id="rId1"/>
     <sheet name="datos" sheetId="2" r:id="rId2"/>
+    <sheet name="Estadisticas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="listaLab">datos!$A$2:$A$10</definedName>
     <definedName name="listaS">datos!$C$2:$C$3</definedName>
     <definedName name="listaServicios">datos!$B$2:$B$10</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="185">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -576,6 +577,39 @@
   </si>
   <si>
     <t>nd9304@unphu.edu.do</t>
+  </si>
+  <si>
+    <t>Consultoría Composición Florística</t>
+  </si>
+  <si>
+    <t>Capacitacion Herbario</t>
+  </si>
+  <si>
+    <t>Consultoría Listados Floristicos</t>
+  </si>
+  <si>
+    <t>Analisis Quimico-Contenido de Polifenoles</t>
+  </si>
+  <si>
+    <t>Análisis Químico-Flavonoides</t>
+  </si>
+  <si>
+    <t>Análisis Químico-HPLC</t>
+  </si>
+  <si>
+    <t>Consultoria-Residuos</t>
+  </si>
+  <si>
+    <t>Consultoria-Quimica</t>
+  </si>
+  <si>
+    <t>Consultoria-Biologicas</t>
+  </si>
+  <si>
+    <t>Laboratorios que prestan servicios:</t>
+  </si>
+  <si>
+    <t>Total Servicios Prestados:</t>
   </si>
 </sst>
 </file>
@@ -649,7 +683,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -671,6 +705,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -968,22 +1003,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="39.140625" customWidth="1"/>
+    <col min="1" max="1" width="64.1796875" customWidth="1"/>
+    <col min="2" max="2" width="50.26953125" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="5" max="5" width="31.54296875" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" customWidth="1"/>
+    <col min="8" max="8" width="39.1796875" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="43.28515625" customWidth="1"/>
+    <col min="10" max="10" width="43.26953125" customWidth="1"/>
     <col min="11" max="11" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +1053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="139.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1026,7 +1061,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1053,7 +1088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1061,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1088,7 +1123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1096,7 +1131,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -1123,7 +1158,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1131,7 +1166,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
         <v>37</v>
@@ -1158,7 +1193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1166,7 +1201,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
@@ -1193,7 +1228,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1201,7 +1236,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1228,7 +1263,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -1236,7 +1271,7 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1263,7 +1298,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1271,7 +1306,7 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -1298,7 +1333,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1306,7 +1341,7 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1333,7 +1368,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1341,7 +1376,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1368,7 +1403,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -1376,7 +1411,7 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1403,7 +1438,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1438,7 +1473,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -1446,7 +1481,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1473,7 +1508,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -1481,7 +1516,7 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
         <v>37</v>
@@ -1508,7 +1543,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -1516,7 +1551,7 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="D16" t="s">
         <v>37</v>
@@ -1543,7 +1578,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1551,7 +1586,7 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -1578,7 +1613,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1586,7 +1621,7 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
         <v>37</v>
@@ -1613,7 +1648,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="232" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -1621,7 +1656,7 @@
         <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1648,7 +1683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="315" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="290" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -1656,7 +1691,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -1683,7 +1718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="225" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1691,7 +1726,7 @@
         <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1718,7 +1753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="225" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -1726,7 +1761,7 @@
         <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1753,7 +1788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="145" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -1788,7 +1823,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="87" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1823,7 +1858,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -1858,7 +1893,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="198" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="198" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>110</v>
       </c>
@@ -1893,7 +1928,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>110</v>
       </c>
@@ -1928,7 +1963,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>110</v>
       </c>
@@ -1963,7 +1998,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>110</v>
       </c>
@@ -1998,7 +2033,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="158.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="158.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>110</v>
       </c>
@@ -2033,7 +2068,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="118.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="118.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>148</v>
       </c>
@@ -2068,7 +2103,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="145.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>148</v>
       </c>
@@ -2103,7 +2138,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="171.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="171.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>148</v>
       </c>
@@ -2154,7 +2189,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A67" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>listaLab</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C57" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C34:C57" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>listaServicios</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D57" xr:uid="{00000000-0002-0000-0000-000002000000}">
@@ -2178,19 +2213,31 @@
     <hyperlink ref="B27:B33" r:id="rId14" display="nd9304@unphu.edu.do" xr:uid="{B87B9367-5431-4996-AA71-F3ABDCA9B1AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{524BA6E6-AA69-495C-AF2E-F2C2C6AECD76}">
+          <x14:formula1>
+            <xm:f>datos!$B$2:$B$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C33</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.140625" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="64.1796875" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2201,7 +2248,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2212,7 +2259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -2223,7 +2270,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -2231,7 +2278,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>109</v>
       </c>
@@ -2239,7 +2286,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>110</v>
       </c>
@@ -2247,7 +2294,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>148</v>
       </c>
@@ -2255,25 +2302,97 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>165</v>
       </c>
     </row>
+    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B13" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B14" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F92528B-A9F8-4251-A9CE-45BA20ED84D3}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="31.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2">
+        <f>COUNTA(datos!A:A)-1</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3">
+        <f>COUNTA(servicios!C:C)-1</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>